--- a/BAS01/项目效益审核表.xlsx
+++ b/BAS01/项目效益审核表.xlsx
@@ -512,7 +512,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="124">
   <si>
     <t xml:space="preserve">            项目效益审核表               单位：元</t>
   </si>
@@ -868,7 +868,7 @@
     <t>八、研发费用</t>
   </si>
   <si>
-    <t>九、成本及费用合计（三+四+五+六+七）</t>
+    <t>九、成本及费用合计（三+四+五+六+七+八）</t>
   </si>
   <si>
     <t>十、增值税实际税负（按财务数据）</t>
@@ -2281,11 +2281,11 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="43" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2856,9 +2856,9 @@
     <col min="2" max="2" width="21.8181818181818" style="5" customWidth="1"/>
     <col min="3" max="3" width="16.7636363636364" style="5" customWidth="1"/>
     <col min="4" max="4" width="37.7545454545455" style="5" customWidth="1"/>
-    <col min="5" max="5" width="35.0545454545455" style="5" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="20" style="5" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="19.1909090909091" style="5" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="35.0545454545455" style="5" customWidth="1"/>
+    <col min="6" max="6" width="20" style="5" customWidth="1"/>
+    <col min="7" max="7" width="19.1909090909091" style="5" customWidth="1"/>
     <col min="8" max="8" width="20.9090909090909" style="5" customWidth="1"/>
     <col min="9" max="9" width="25.2545454545455" style="5" customWidth="1"/>
     <col min="10" max="11" width="20.9090909090909" style="5" customWidth="1"/>
@@ -3215,7 +3215,10 @@
         <f>M6+N6+O6+P6</f>
         <v>0</v>
       </c>
-      <c r="S6" s="83"/>
+      <c r="S6" s="83">
+        <f>SUM(T6+U6+V6)</f>
+        <v>0</v>
+      </c>
       <c r="T6" s="83"/>
       <c r="U6" s="83"/>
       <c r="V6" s="83"/>
@@ -3242,7 +3245,7 @@
       </c>
       <c r="AL6" s="21"/>
     </row>
-    <row r="7" ht="14" spans="1:38">
+    <row r="7" spans="1:38">
       <c r="A7" s="13"/>
       <c r="B7" s="14" t="s">
         <v>48</v>
@@ -3400,7 +3403,7 @@
       </c>
       <c r="AL8" s="28"/>
     </row>
-    <row r="9" spans="1:38">
+    <row r="9" ht="14" spans="1:38">
       <c r="A9" s="30"/>
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
@@ -3615,11 +3618,17 @@
       <c r="P12" s="75"/>
       <c r="Q12" s="75"/>
       <c r="R12" s="75"/>
-      <c r="S12" s="36"/>
+      <c r="S12" s="36">
+        <f t="shared" ref="S12:S15" si="0">SUM(T12:V12)</f>
+        <v>0</v>
+      </c>
       <c r="T12" s="36"/>
       <c r="U12" s="36"/>
       <c r="V12" s="36"/>
-      <c r="W12" s="36"/>
+      <c r="W12" s="36">
+        <f t="shared" ref="W12:W15" si="1">SUM(X12:Y12)</f>
+        <v>0</v>
+      </c>
       <c r="X12" s="36"/>
       <c r="Y12" s="36"/>
       <c r="Z12" s="36"/>
@@ -3649,37 +3658,43 @@
       <c r="H13" s="36"/>
       <c r="I13" s="36"/>
       <c r="J13" s="75">
-        <f t="shared" ref="J13:J15" si="0">H13+I13</f>
+        <f t="shared" ref="J13:J15" si="2">H13+I13</f>
         <v>0</v>
       </c>
       <c r="K13" s="36"/>
       <c r="L13" s="75">
-        <f t="shared" ref="L13:L15" si="1">J13-K13</f>
+        <f t="shared" ref="L13:L15" si="3">J13-K13</f>
         <v>0</v>
       </c>
       <c r="M13" s="36"/>
       <c r="N13" s="36"/>
       <c r="O13" s="75">
-        <f t="shared" ref="O13:O15" si="2">L13-M13</f>
+        <f t="shared" ref="O13:O15" si="4">L13-M13</f>
         <v>0</v>
       </c>
       <c r="P13" s="75">
-        <f t="shared" ref="P13:P15" si="3">K13-N13</f>
+        <f t="shared" ref="P13:P15" si="5">K13-N13</f>
         <v>0</v>
       </c>
       <c r="Q13" s="75">
-        <f t="shared" ref="Q13:Q15" si="4">M13+O13</f>
+        <f t="shared" ref="Q13:Q15" si="6">M13+O13</f>
         <v>0</v>
       </c>
       <c r="R13" s="75">
-        <f t="shared" ref="R13:R15" si="5">M13+N13+O13+P13</f>
-        <v>0</v>
-      </c>
-      <c r="S13" s="36"/>
+        <f t="shared" ref="R13:R15" si="7">M13+N13+O13+P13</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="T13" s="36"/>
       <c r="U13" s="36"/>
       <c r="V13" s="36"/>
-      <c r="W13" s="36"/>
+      <c r="W13" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="X13" s="36"/>
       <c r="Y13" s="36"/>
       <c r="Z13" s="36"/>
@@ -3709,37 +3724,43 @@
       <c r="H14" s="36"/>
       <c r="I14" s="36"/>
       <c r="J14" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K14" s="36"/>
       <c r="L14" s="75">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M14" s="36"/>
       <c r="N14" s="36"/>
       <c r="O14" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P14" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q14" s="75">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R14" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S14" s="36"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S14" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="T14" s="36"/>
       <c r="U14" s="36"/>
       <c r="V14" s="36"/>
-      <c r="W14" s="36"/>
+      <c r="W14" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="X14" s="36"/>
       <c r="Y14" s="36"/>
       <c r="Z14" s="36"/>
@@ -3769,37 +3790,43 @@
       <c r="H15" s="36"/>
       <c r="I15" s="36"/>
       <c r="J15" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K15" s="36"/>
       <c r="L15" s="75">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M15" s="36"/>
       <c r="N15" s="36"/>
       <c r="O15" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P15" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q15" s="75">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R15" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S15" s="36"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="T15" s="36"/>
       <c r="U15" s="36"/>
       <c r="V15" s="36"/>
-      <c r="W15" s="36"/>
+      <c r="W15" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="X15" s="36"/>
       <c r="Y15" s="36"/>
       <c r="Z15" s="36"/>
@@ -3869,123 +3896,123 @@
       <c r="F17" s="44"/>
       <c r="G17" s="44"/>
       <c r="H17" s="44">
-        <f t="shared" ref="H17:AK17" si="6">SUM(H12:H16)</f>
+        <f t="shared" ref="H17:AK17" si="8">SUM(H12:H16)</f>
         <v>0</v>
       </c>
       <c r="I17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J17" s="76">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L17" s="76">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="N17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O17" s="76">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="P17" s="76">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q17" s="76">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R17" s="76">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Y17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Z17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AA17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AB17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AC17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AD17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AF17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AG17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AI17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AK17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AL17" s="96"/>
@@ -4045,37 +4072,43 @@
       <c r="H19" s="36"/>
       <c r="I19" s="36"/>
       <c r="J19" s="75">
-        <f t="shared" ref="J19:J21" si="7">H19+I19</f>
+        <f t="shared" ref="J19:J21" si="9">H19+I19</f>
         <v>0</v>
       </c>
       <c r="K19" s="36"/>
       <c r="L19" s="75">
-        <f t="shared" ref="L19:L21" si="8">J19-K19</f>
+        <f t="shared" ref="L19:L21" si="10">J19-K19</f>
         <v>0</v>
       </c>
       <c r="M19" s="36"/>
       <c r="N19" s="36"/>
       <c r="O19" s="75">
-        <f t="shared" ref="O19:O21" si="9">L19-M19</f>
+        <f t="shared" ref="O19:O21" si="11">L19-M19</f>
         <v>0</v>
       </c>
       <c r="P19" s="75">
-        <f t="shared" ref="P19:P21" si="10">K19-N19</f>
+        <f t="shared" ref="P19:P21" si="12">K19-N19</f>
         <v>0</v>
       </c>
       <c r="Q19" s="75">
-        <f t="shared" ref="Q19:Q21" si="11">M19+O19</f>
+        <f t="shared" ref="Q19:Q21" si="13">M19+O19</f>
         <v>0</v>
       </c>
       <c r="R19" s="75">
-        <f t="shared" ref="R19:R21" si="12">M19+N19+O19+P19</f>
-        <v>0</v>
-      </c>
-      <c r="S19" s="36"/>
+        <f t="shared" ref="R19:R21" si="14">M19+N19+O19+P19</f>
+        <v>0</v>
+      </c>
+      <c r="S19" s="36">
+        <f t="shared" ref="S19:S21" si="15">SUM(T19:V19)</f>
+        <v>0</v>
+      </c>
       <c r="T19" s="36"/>
       <c r="U19" s="36"/>
       <c r="V19" s="36"/>
-      <c r="W19" s="36"/>
+      <c r="W19" s="36">
+        <f t="shared" ref="W19:W21" si="16">SUM(X19:Y19)</f>
+        <v>0</v>
+      </c>
       <c r="X19" s="36"/>
       <c r="Y19" s="36"/>
       <c r="Z19" s="36"/>
@@ -4105,37 +4138,43 @@
       <c r="H20" s="36"/>
       <c r="I20" s="36"/>
       <c r="J20" s="75">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K20" s="36"/>
       <c r="L20" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M20" s="36"/>
       <c r="N20" s="36"/>
       <c r="O20" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P20" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q20" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R20" s="75">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S20" s="36"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="36">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="T20" s="36"/>
       <c r="U20" s="36"/>
       <c r="V20" s="36"/>
-      <c r="W20" s="36"/>
+      <c r="W20" s="36">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
       <c r="X20" s="36"/>
       <c r="Y20" s="36"/>
       <c r="Z20" s="36"/>
@@ -4165,37 +4204,43 @@
       <c r="H21" s="36"/>
       <c r="I21" s="36"/>
       <c r="J21" s="75">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K21" s="36"/>
       <c r="L21" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M21" s="36"/>
       <c r="N21" s="36"/>
       <c r="O21" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P21" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q21" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R21" s="75">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S21" s="36"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="36">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="T21" s="36"/>
       <c r="U21" s="36"/>
       <c r="V21" s="36"/>
-      <c r="W21" s="36"/>
+      <c r="W21" s="36">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
       <c r="X21" s="36"/>
       <c r="Y21" s="36"/>
       <c r="Z21" s="36"/>
@@ -4265,123 +4310,123 @@
       <c r="F23" s="44"/>
       <c r="G23" s="44"/>
       <c r="H23" s="44">
-        <f t="shared" ref="H23:AK23" si="13">SUM(H19:H22)</f>
+        <f t="shared" ref="H23:AK23" si="17">SUM(H19:H22)</f>
         <v>0</v>
       </c>
       <c r="I23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="J23" s="76">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="K23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="L23" s="76">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O23" s="76">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P23" s="76">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Q23" s="76">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="R23" s="76">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="S23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="T23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="U23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="V23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="W23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="X23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Y23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Z23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AA23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AB23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AC23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AD23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AE23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AF23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AG23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AH23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AI23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AJ23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AL23" s="96"/>
@@ -4483,37 +4528,43 @@
       <c r="H26" s="36"/>
       <c r="I26" s="36"/>
       <c r="J26" s="75">
-        <f t="shared" ref="J26:J28" si="14">H26+I26</f>
+        <f t="shared" ref="J26:J28" si="18">H26+I26</f>
         <v>0</v>
       </c>
       <c r="K26" s="36"/>
       <c r="L26" s="75">
-        <f t="shared" ref="L26:L28" si="15">J26-K26</f>
+        <f t="shared" ref="L26:L28" si="19">J26-K26</f>
         <v>0</v>
       </c>
       <c r="M26" s="36"/>
       <c r="N26" s="36"/>
       <c r="O26" s="75">
-        <f t="shared" ref="O26:O28" si="16">L26-M26</f>
+        <f t="shared" ref="O26:O28" si="20">L26-M26</f>
         <v>0</v>
       </c>
       <c r="P26" s="75">
-        <f t="shared" ref="P26:P28" si="17">K26-N26</f>
+        <f t="shared" ref="P26:P28" si="21">K26-N26</f>
         <v>0</v>
       </c>
       <c r="Q26" s="75">
-        <f t="shared" ref="Q26:Q32" si="18">M26+O26</f>
+        <f t="shared" ref="Q26:Q32" si="22">M26+O26</f>
         <v>0</v>
       </c>
       <c r="R26" s="75">
-        <f t="shared" ref="R26:R32" si="19">M26+N26+O26+P26</f>
-        <v>0</v>
-      </c>
-      <c r="S26" s="36"/>
+        <f t="shared" ref="R26:R32" si="23">M26+N26+O26+P26</f>
+        <v>0</v>
+      </c>
+      <c r="S26" s="36">
+        <f t="shared" ref="S26:S32" si="24">SUM(T26:V26)</f>
+        <v>0</v>
+      </c>
       <c r="T26" s="36"/>
       <c r="U26" s="36"/>
       <c r="V26" s="36"/>
-      <c r="W26" s="36"/>
+      <c r="W26" s="36">
+        <f t="shared" ref="W26:W32" si="25">SUM(X26:Y26)</f>
+        <v>0</v>
+      </c>
       <c r="X26" s="36"/>
       <c r="Y26" s="36"/>
       <c r="Z26" s="36"/>
@@ -4543,37 +4594,43 @@
       <c r="H27" s="36"/>
       <c r="I27" s="36"/>
       <c r="J27" s="75">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="K27" s="36"/>
       <c r="L27" s="75">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M27" s="36"/>
       <c r="N27" s="36"/>
       <c r="O27" s="75">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="P27" s="75">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="Q27" s="75">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="R27" s="75">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="S27" s="36"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="36">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="T27" s="36"/>
       <c r="U27" s="36"/>
       <c r="V27" s="36"/>
-      <c r="W27" s="36"/>
+      <c r="W27" s="36">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="X27" s="36"/>
       <c r="Y27" s="36"/>
       <c r="Z27" s="36"/>
@@ -4603,37 +4660,43 @@
       <c r="H28" s="36"/>
       <c r="I28" s="36"/>
       <c r="J28" s="75">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="K28" s="36"/>
       <c r="L28" s="75">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M28" s="36"/>
       <c r="N28" s="36"/>
       <c r="O28" s="75">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="P28" s="75">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="Q28" s="75">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="R28" s="75">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="S28" s="36"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="36">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="T28" s="36"/>
       <c r="U28" s="36"/>
       <c r="V28" s="36"/>
-      <c r="W28" s="36"/>
+      <c r="W28" s="36">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="X28" s="36"/>
       <c r="Y28" s="36"/>
       <c r="Z28" s="36"/>
@@ -4670,18 +4733,24 @@
       <c r="O29" s="75"/>
       <c r="P29" s="75"/>
       <c r="Q29" s="75">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="R29" s="75">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="S29" s="36"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="36">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="T29" s="36"/>
       <c r="U29" s="36"/>
       <c r="V29" s="36"/>
-      <c r="W29" s="36"/>
+      <c r="W29" s="36">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="X29" s="36"/>
       <c r="Y29" s="36"/>
       <c r="Z29" s="36"/>
@@ -4713,37 +4782,43 @@
       <c r="H30" s="36"/>
       <c r="I30" s="36"/>
       <c r="J30" s="75">
-        <f t="shared" ref="J30:J32" si="20">H30+I30</f>
+        <f t="shared" ref="J30:J32" si="26">H30+I30</f>
         <v>0</v>
       </c>
       <c r="K30" s="36"/>
       <c r="L30" s="75">
-        <f t="shared" ref="L30:L32" si="21">J30-K30</f>
+        <f t="shared" ref="L30:L32" si="27">J30-K30</f>
         <v>0</v>
       </c>
       <c r="M30" s="36"/>
       <c r="N30" s="36"/>
       <c r="O30" s="75">
-        <f t="shared" ref="O30:O32" si="22">L30-M30</f>
+        <f t="shared" ref="O30:O32" si="28">L30-M30</f>
         <v>0</v>
       </c>
       <c r="P30" s="75">
-        <f t="shared" ref="P30:P32" si="23">K30-N30</f>
+        <f t="shared" ref="P30:P32" si="29">K30-N30</f>
         <v>0</v>
       </c>
       <c r="Q30" s="75">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="R30" s="75">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="S30" s="36"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="36">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="T30" s="36"/>
       <c r="U30" s="36"/>
       <c r="V30" s="36"/>
-      <c r="W30" s="36"/>
+      <c r="W30" s="36">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="X30" s="36"/>
       <c r="Y30" s="36"/>
       <c r="Z30" s="36"/>
@@ -4775,37 +4850,43 @@
       <c r="H31" s="50"/>
       <c r="I31" s="50"/>
       <c r="J31" s="75">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="K31" s="50"/>
       <c r="L31" s="75">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="M31" s="50"/>
       <c r="N31" s="50"/>
       <c r="O31" s="75">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="P31" s="75">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="75">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="P31" s="75">
+      <c r="R31" s="75">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="Q31" s="75">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="R31" s="75">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="S31" s="50"/>
+      <c r="S31" s="36">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="T31" s="50"/>
       <c r="U31" s="50"/>
       <c r="V31" s="50"/>
-      <c r="W31" s="50"/>
+      <c r="W31" s="36">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="X31" s="50"/>
       <c r="Y31" s="50"/>
       <c r="Z31" s="50"/>
@@ -4837,37 +4918,43 @@
       <c r="H32" s="50"/>
       <c r="I32" s="50"/>
       <c r="J32" s="75">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="K32" s="50"/>
       <c r="L32" s="75">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="M32" s="50"/>
       <c r="N32" s="50"/>
       <c r="O32" s="75">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="P32" s="75">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="Q32" s="75">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="P32" s="75">
+      <c r="R32" s="75">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="Q32" s="75">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="R32" s="75">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="S32" s="50"/>
+      <c r="S32" s="36">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="T32" s="50"/>
       <c r="U32" s="50"/>
       <c r="V32" s="50"/>
-      <c r="W32" s="50"/>
+      <c r="W32" s="36">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="X32" s="50"/>
       <c r="Y32" s="50"/>
       <c r="Z32" s="50"/>
@@ -4937,123 +5024,123 @@
       <c r="F34" s="44"/>
       <c r="G34" s="44"/>
       <c r="H34" s="44">
-        <f t="shared" ref="H34:AK34" si="24">SUM(H25:H33)</f>
+        <f t="shared" ref="H34:AK34" si="30">SUM(H25:H33)</f>
         <v>0</v>
       </c>
       <c r="I34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="J34" s="76">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="L34" s="76">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="N34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="O34" s="76">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="P34" s="76">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Q34" s="76">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="R34" s="76">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="S34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="T34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="U34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="V34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="W34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="X34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Y34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AA34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AB34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AC34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AD34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AE34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AF34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AG34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AH34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AI34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AJ34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AK34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AL34" s="96"/>
@@ -5113,37 +5200,43 @@
       <c r="H36" s="36"/>
       <c r="I36" s="36"/>
       <c r="J36" s="75">
-        <f t="shared" ref="J36:J44" si="25">H36+I36</f>
+        <f t="shared" ref="J36:J44" si="31">H36+I36</f>
         <v>0</v>
       </c>
       <c r="K36" s="36"/>
       <c r="L36" s="75">
-        <f t="shared" ref="L36:L44" si="26">J36-K36</f>
+        <f t="shared" ref="L36:L44" si="32">J36-K36</f>
         <v>0</v>
       </c>
       <c r="M36" s="36"/>
       <c r="N36" s="36"/>
       <c r="O36" s="75">
-        <f t="shared" ref="O36:O44" si="27">L36-M36</f>
+        <f t="shared" ref="O36:O44" si="33">L36-M36</f>
         <v>0</v>
       </c>
       <c r="P36" s="75">
-        <f t="shared" ref="P36:P44" si="28">K36-N36</f>
+        <f t="shared" ref="P36:P44" si="34">K36-N36</f>
         <v>0</v>
       </c>
       <c r="Q36" s="75">
-        <f t="shared" ref="Q36:Q44" si="29">M36+O36</f>
+        <f t="shared" ref="Q36:Q44" si="35">M36+O36</f>
         <v>0</v>
       </c>
       <c r="R36" s="75">
-        <f t="shared" ref="R36:R44" si="30">M36+N36+O36+P36</f>
-        <v>0</v>
-      </c>
-      <c r="S36" s="36"/>
+        <f t="shared" ref="R36:R44" si="36">M36+N36+O36+P36</f>
+        <v>0</v>
+      </c>
+      <c r="S36" s="36">
+        <f t="shared" ref="S36:S44" si="37">SUM(T36:V36)</f>
+        <v>0</v>
+      </c>
       <c r="T36" s="36"/>
       <c r="U36" s="36"/>
       <c r="V36" s="36"/>
-      <c r="W36" s="36"/>
+      <c r="W36" s="36">
+        <f t="shared" ref="W36:W44" si="38">SUM(X36:Y36)</f>
+        <v>0</v>
+      </c>
       <c r="X36" s="36"/>
       <c r="Y36" s="36"/>
       <c r="Z36" s="36"/>
@@ -5213,123 +5306,123 @@
       <c r="F38" s="54"/>
       <c r="G38" s="54"/>
       <c r="H38" s="44">
-        <f t="shared" ref="H38:AK38" si="31">SUM(H36:H37)</f>
+        <f t="shared" ref="H38:AK38" si="39">SUM(H36:H37)</f>
         <v>0</v>
       </c>
       <c r="I38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="J38" s="76">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="K38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="L38" s="76">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="M38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="N38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="O38" s="76">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="P38" s="76">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="Q38" s="76">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="R38" s="76">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="S38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="T38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="U38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="W38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="X38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="Y38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="Z38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AA38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AB38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AC38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AD38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AE38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AF38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AG38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AH38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AI38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AJ38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AK38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AL38" s="96"/>
@@ -5389,37 +5482,43 @@
       <c r="H40" s="36"/>
       <c r="I40" s="36"/>
       <c r="J40" s="75">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="K40" s="36"/>
       <c r="L40" s="75">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="M40" s="36"/>
       <c r="N40" s="36"/>
       <c r="O40" s="75">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="P40" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Q40" s="75">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="R40" s="75">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="S40" s="36"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="36">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="T40" s="36"/>
       <c r="U40" s="36"/>
       <c r="V40" s="36"/>
-      <c r="W40" s="36"/>
+      <c r="W40" s="36">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
       <c r="X40" s="36"/>
       <c r="Y40" s="36"/>
       <c r="Z40" s="36"/>
@@ -5449,37 +5548,43 @@
       <c r="H41" s="36"/>
       <c r="I41" s="36"/>
       <c r="J41" s="75">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="K41" s="36"/>
       <c r="L41" s="75">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="M41" s="36"/>
       <c r="N41" s="36"/>
       <c r="O41" s="75">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="P41" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Q41" s="75">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="R41" s="75">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="S41" s="36"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="36">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="T41" s="36"/>
       <c r="U41" s="36"/>
       <c r="V41" s="36"/>
-      <c r="W41" s="36"/>
+      <c r="W41" s="36">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
       <c r="X41" s="36"/>
       <c r="Y41" s="36"/>
       <c r="Z41" s="36"/>
@@ -5509,37 +5614,43 @@
       <c r="H42" s="36"/>
       <c r="I42" s="36"/>
       <c r="J42" s="75">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="K42" s="36"/>
       <c r="L42" s="75">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="M42" s="36"/>
       <c r="N42" s="36"/>
       <c r="O42" s="75">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="P42" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Q42" s="75">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="R42" s="75">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="S42" s="36"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="S42" s="36">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="T42" s="36"/>
       <c r="U42" s="36"/>
       <c r="V42" s="36"/>
-      <c r="W42" s="36"/>
+      <c r="W42" s="36">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
       <c r="X42" s="36"/>
       <c r="Y42" s="36"/>
       <c r="Z42" s="36"/>
@@ -5569,37 +5680,43 @@
       <c r="H43" s="36"/>
       <c r="I43" s="36"/>
       <c r="J43" s="75">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="K43" s="36"/>
       <c r="L43" s="75">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="M43" s="36"/>
       <c r="N43" s="36"/>
       <c r="O43" s="75">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="P43" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Q43" s="75">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="R43" s="75">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="S43" s="36"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="36">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="T43" s="36"/>
       <c r="U43" s="36"/>
       <c r="V43" s="36"/>
-      <c r="W43" s="36"/>
+      <c r="W43" s="36">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
       <c r="X43" s="36"/>
       <c r="Y43" s="36"/>
       <c r="Z43" s="36"/>
@@ -5629,37 +5746,43 @@
       <c r="H44" s="36"/>
       <c r="I44" s="36"/>
       <c r="J44" s="75">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="K44" s="36"/>
       <c r="L44" s="75">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="M44" s="36"/>
       <c r="N44" s="36"/>
       <c r="O44" s="75">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="P44" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Q44" s="75">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="R44" s="75">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="S44" s="36"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="S44" s="36">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="T44" s="36"/>
       <c r="U44" s="36"/>
       <c r="V44" s="36"/>
-      <c r="W44" s="36"/>
+      <c r="W44" s="36">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
       <c r="X44" s="36"/>
       <c r="Y44" s="36"/>
       <c r="Z44" s="36"/>
@@ -5729,123 +5852,123 @@
       <c r="F46" s="57"/>
       <c r="G46" s="57"/>
       <c r="H46" s="44">
-        <f t="shared" ref="H46:AK46" si="32">SUM(H40:H45)</f>
+        <f t="shared" ref="H46:AK46" si="40">SUM(H40:H45)</f>
         <v>0</v>
       </c>
       <c r="I46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="J46" s="76">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="K46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="L46" s="76">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="M46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="N46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="O46" s="76">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="P46" s="76">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="Q46" s="76">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="R46" s="76">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="S46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="T46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="U46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="V46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="W46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="X46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="Y46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="Z46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AA46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AB46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AC46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AD46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AE46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AF46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AG46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AH46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AI46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AJ46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AK46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AL46" s="96"/>
@@ -5905,37 +6028,43 @@
       <c r="H48" s="59"/>
       <c r="I48" s="59"/>
       <c r="J48" s="75">
-        <f t="shared" ref="J48:J59" si="33">H48+I48</f>
+        <f t="shared" ref="J48:J59" si="41">H48+I48</f>
         <v>0</v>
       </c>
       <c r="K48" s="59"/>
       <c r="L48" s="75">
-        <f t="shared" ref="L48:L59" si="34">J48-K48</f>
+        <f t="shared" ref="L48:L59" si="42">J48-K48</f>
         <v>0</v>
       </c>
       <c r="M48" s="59"/>
       <c r="N48" s="59"/>
       <c r="O48" s="75">
-        <f t="shared" ref="O48:O59" si="35">L48-M48</f>
+        <f t="shared" ref="O48:O59" si="43">L48-M48</f>
         <v>0</v>
       </c>
       <c r="P48" s="75">
-        <f t="shared" ref="P48:P59" si="36">K48-N48</f>
+        <f t="shared" ref="P48:P59" si="44">K48-N48</f>
         <v>0</v>
       </c>
       <c r="Q48" s="75">
-        <f t="shared" ref="Q48:Q59" si="37">M48+O48</f>
+        <f t="shared" ref="Q48:Q59" si="45">M48+O48</f>
         <v>0</v>
       </c>
       <c r="R48" s="75">
-        <f t="shared" ref="R48:R59" si="38">M48+N48+O48+P48</f>
-        <v>0</v>
-      </c>
-      <c r="S48" s="59"/>
+        <f t="shared" ref="R48:R59" si="46">M48+N48+O48+P48</f>
+        <v>0</v>
+      </c>
+      <c r="S48" s="36">
+        <f t="shared" ref="S48:S59" si="47">SUM(T48:V48)</f>
+        <v>0</v>
+      </c>
       <c r="T48" s="59"/>
       <c r="U48" s="59"/>
       <c r="V48" s="59"/>
-      <c r="W48" s="59"/>
+      <c r="W48" s="36">
+        <f t="shared" ref="W48:W59" si="48">SUM(X48:Y48)</f>
+        <v>0</v>
+      </c>
       <c r="X48" s="59"/>
       <c r="Y48" s="59"/>
       <c r="Z48" s="59"/>
@@ -5965,37 +6094,43 @@
       <c r="H49" s="59"/>
       <c r="I49" s="59"/>
       <c r="J49" s="75">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K49" s="59"/>
       <c r="L49" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M49" s="59"/>
       <c r="N49" s="59"/>
       <c r="O49" s="75">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P49" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="Q49" s="75">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="R49" s="75">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S49" s="59"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="36">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
       <c r="T49" s="59"/>
       <c r="U49" s="59"/>
       <c r="V49" s="59"/>
-      <c r="W49" s="59"/>
+      <c r="W49" s="36">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="X49" s="59"/>
       <c r="Y49" s="59"/>
       <c r="Z49" s="59"/>
@@ -6025,37 +6160,43 @@
       <c r="H50" s="59"/>
       <c r="I50" s="59"/>
       <c r="J50" s="75">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K50" s="59"/>
       <c r="L50" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M50" s="59"/>
       <c r="N50" s="59"/>
       <c r="O50" s="75">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P50" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="Q50" s="75">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="R50" s="75">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S50" s="59"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="36">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
       <c r="T50" s="59"/>
       <c r="U50" s="59"/>
       <c r="V50" s="59"/>
-      <c r="W50" s="59"/>
+      <c r="W50" s="36">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="X50" s="59"/>
       <c r="Y50" s="59"/>
       <c r="Z50" s="59"/>
@@ -6085,37 +6226,43 @@
       <c r="H51" s="59"/>
       <c r="I51" s="59"/>
       <c r="J51" s="75">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K51" s="59"/>
       <c r="L51" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M51" s="59"/>
       <c r="N51" s="59"/>
       <c r="O51" s="75">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P51" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="Q51" s="75">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="R51" s="75">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S51" s="59"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="36">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
       <c r="T51" s="59"/>
       <c r="U51" s="59"/>
       <c r="V51" s="59"/>
-      <c r="W51" s="59"/>
+      <c r="W51" s="36">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="X51" s="59"/>
       <c r="Y51" s="59"/>
       <c r="Z51" s="59"/>
@@ -6145,37 +6292,43 @@
       <c r="H52" s="59"/>
       <c r="I52" s="59"/>
       <c r="J52" s="75">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K52" s="59"/>
       <c r="L52" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M52" s="59"/>
       <c r="N52" s="59"/>
       <c r="O52" s="75">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P52" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="Q52" s="75">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="R52" s="75">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S52" s="59"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="36">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
       <c r="T52" s="59"/>
       <c r="U52" s="59"/>
       <c r="V52" s="59"/>
-      <c r="W52" s="59"/>
+      <c r="W52" s="36">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="X52" s="59"/>
       <c r="Y52" s="59"/>
       <c r="Z52" s="59"/>
@@ -6205,37 +6358,43 @@
       <c r="H53" s="59"/>
       <c r="I53" s="59"/>
       <c r="J53" s="75">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K53" s="59"/>
       <c r="L53" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M53" s="59"/>
       <c r="N53" s="59"/>
       <c r="O53" s="75">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P53" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="Q53" s="75">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="R53" s="75">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S53" s="59"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="36">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
       <c r="T53" s="59"/>
       <c r="U53" s="59"/>
       <c r="V53" s="59"/>
-      <c r="W53" s="59"/>
+      <c r="W53" s="36">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="X53" s="59"/>
       <c r="Y53" s="59"/>
       <c r="Z53" s="59"/>
@@ -6265,37 +6424,43 @@
       <c r="H54" s="59"/>
       <c r="I54" s="59"/>
       <c r="J54" s="75">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K54" s="59"/>
       <c r="L54" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M54" s="59"/>
       <c r="N54" s="59"/>
       <c r="O54" s="75">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P54" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="Q54" s="75">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="R54" s="75">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S54" s="59"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="36">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
       <c r="T54" s="59"/>
       <c r="U54" s="59"/>
       <c r="V54" s="59"/>
-      <c r="W54" s="59"/>
+      <c r="W54" s="36">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="X54" s="59"/>
       <c r="Y54" s="59"/>
       <c r="Z54" s="59"/>
@@ -6325,37 +6490,43 @@
       <c r="H55" s="59"/>
       <c r="I55" s="59"/>
       <c r="J55" s="75">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K55" s="59"/>
       <c r="L55" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M55" s="59"/>
       <c r="N55" s="59"/>
       <c r="O55" s="75">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P55" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="Q55" s="75">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="R55" s="75">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S55" s="59"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="36">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
       <c r="T55" s="59"/>
       <c r="U55" s="59"/>
       <c r="V55" s="59"/>
-      <c r="W55" s="59"/>
+      <c r="W55" s="36">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="X55" s="59"/>
       <c r="Y55" s="59"/>
       <c r="Z55" s="59"/>
@@ -6385,37 +6556,43 @@
       <c r="H56" s="59"/>
       <c r="I56" s="59"/>
       <c r="J56" s="75">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K56" s="59"/>
       <c r="L56" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M56" s="59"/>
       <c r="N56" s="59"/>
       <c r="O56" s="75">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P56" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="Q56" s="75">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="R56" s="75">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S56" s="59"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="36">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
       <c r="T56" s="59"/>
       <c r="U56" s="59"/>
       <c r="V56" s="59"/>
-      <c r="W56" s="59"/>
+      <c r="W56" s="36">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="X56" s="59"/>
       <c r="Y56" s="59"/>
       <c r="Z56" s="59"/>
@@ -6445,37 +6622,43 @@
       <c r="H57" s="59"/>
       <c r="I57" s="59"/>
       <c r="J57" s="75">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K57" s="59"/>
       <c r="L57" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M57" s="59"/>
       <c r="N57" s="59"/>
       <c r="O57" s="75">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P57" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="Q57" s="75">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="R57" s="75">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S57" s="59"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="36">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
       <c r="T57" s="59"/>
       <c r="U57" s="59"/>
       <c r="V57" s="59"/>
-      <c r="W57" s="59"/>
+      <c r="W57" s="36">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="X57" s="59"/>
       <c r="Y57" s="59"/>
       <c r="Z57" s="59"/>
@@ -6505,37 +6688,43 @@
       <c r="H58" s="59"/>
       <c r="I58" s="59"/>
       <c r="J58" s="75">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K58" s="59"/>
       <c r="L58" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M58" s="59"/>
       <c r="N58" s="59"/>
       <c r="O58" s="75">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P58" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="Q58" s="75">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="R58" s="75">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S58" s="59"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="36">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
       <c r="T58" s="59"/>
       <c r="U58" s="59"/>
       <c r="V58" s="59"/>
-      <c r="W58" s="59"/>
+      <c r="W58" s="36">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="X58" s="59"/>
       <c r="Y58" s="59"/>
       <c r="Z58" s="59"/>
@@ -6565,37 +6754,43 @@
       <c r="H59" s="59"/>
       <c r="I59" s="59"/>
       <c r="J59" s="75">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K59" s="59"/>
       <c r="L59" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M59" s="59"/>
       <c r="N59" s="59"/>
       <c r="O59" s="75">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P59" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="Q59" s="75">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="R59" s="75">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S59" s="59"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="36">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
       <c r="T59" s="59"/>
       <c r="U59" s="59"/>
       <c r="V59" s="59"/>
-      <c r="W59" s="59"/>
+      <c r="W59" s="36">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="X59" s="59"/>
       <c r="Y59" s="59"/>
       <c r="Z59" s="59"/>
@@ -6665,123 +6860,123 @@
       <c r="F61" s="57"/>
       <c r="G61" s="57"/>
       <c r="H61" s="44">
-        <f t="shared" ref="H61:AK61" si="39">SUM(H48:H60)</f>
+        <f t="shared" ref="H61:AK61" si="49">SUM(H48:H60)</f>
         <v>0</v>
       </c>
       <c r="I61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="J61" s="76">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="K61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="L61" s="76">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="M61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="N61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="O61" s="76">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="P61" s="76">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="Q61" s="76">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="R61" s="76">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="S61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="T61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="U61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="V61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="W61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="X61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="Y61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="Z61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AA61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AB61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AC61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AD61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AE61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AF61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AG61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AH61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AI61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AJ61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AK61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AL61" s="97"/>
@@ -6841,37 +7036,43 @@
       <c r="H63" s="36"/>
       <c r="I63" s="36"/>
       <c r="J63" s="75">
-        <f t="shared" ref="J63:J66" si="40">H63+I63</f>
+        <f t="shared" ref="J63:J66" si="50">H63+I63</f>
         <v>0</v>
       </c>
       <c r="K63" s="36"/>
       <c r="L63" s="75">
-        <f t="shared" ref="L63:L66" si="41">J63-K63</f>
+        <f t="shared" ref="L63:L66" si="51">J63-K63</f>
         <v>0</v>
       </c>
       <c r="M63" s="36"/>
       <c r="N63" s="36"/>
       <c r="O63" s="75">
-        <f t="shared" ref="O63:O66" si="42">L63-M63</f>
+        <f t="shared" ref="O63:O66" si="52">L63-M63</f>
         <v>0</v>
       </c>
       <c r="P63" s="75">
-        <f t="shared" ref="P63:P66" si="43">K63-N63</f>
+        <f t="shared" ref="P63:P66" si="53">K63-N63</f>
         <v>0</v>
       </c>
       <c r="Q63" s="75">
-        <f t="shared" ref="Q63:Q66" si="44">M63+O63</f>
+        <f t="shared" ref="Q63:Q66" si="54">M63+O63</f>
         <v>0</v>
       </c>
       <c r="R63" s="75">
-        <f t="shared" ref="R63:R66" si="45">M63+N63+O63+P63</f>
-        <v>0</v>
-      </c>
-      <c r="S63" s="36"/>
+        <f t="shared" ref="R63:R66" si="55">M63+N63+O63+P63</f>
+        <v>0</v>
+      </c>
+      <c r="S63" s="36">
+        <f t="shared" ref="S63:S66" si="56">SUM(T63:V63)</f>
+        <v>0</v>
+      </c>
       <c r="T63" s="36"/>
       <c r="U63" s="36"/>
       <c r="V63" s="36"/>
-      <c r="W63" s="36"/>
+      <c r="W63" s="36">
+        <f t="shared" ref="W63:W66" si="57">SUM(X63:Y63)</f>
+        <v>0</v>
+      </c>
       <c r="X63" s="36"/>
       <c r="Y63" s="36"/>
       <c r="Z63" s="36"/>
@@ -6901,37 +7102,43 @@
       <c r="H64" s="36"/>
       <c r="I64" s="36"/>
       <c r="J64" s="75">
-        <f t="shared" si="40"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="K64" s="36"/>
       <c r="L64" s="75">
-        <f t="shared" si="41"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M64" s="36"/>
       <c r="N64" s="36"/>
       <c r="O64" s="75">
-        <f t="shared" si="42"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="P64" s="75">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="Q64" s="75">
-        <f t="shared" si="44"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="R64" s="75">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="S64" s="36"/>
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="S64" s="36">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
       <c r="T64" s="36"/>
       <c r="U64" s="36"/>
       <c r="V64" s="36"/>
-      <c r="W64" s="36"/>
+      <c r="W64" s="36">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
       <c r="X64" s="36"/>
       <c r="Y64" s="36"/>
       <c r="Z64" s="36"/>
@@ -6961,37 +7168,43 @@
       <c r="H65" s="36"/>
       <c r="I65" s="36"/>
       <c r="J65" s="75">
-        <f t="shared" si="40"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="K65" s="36"/>
       <c r="L65" s="75">
-        <f t="shared" si="41"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M65" s="36"/>
       <c r="N65" s="36"/>
       <c r="O65" s="75">
-        <f t="shared" si="42"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="P65" s="75">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="Q65" s="75">
-        <f t="shared" si="44"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="R65" s="75">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="S65" s="36"/>
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="S65" s="36">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
       <c r="T65" s="36"/>
       <c r="U65" s="36"/>
       <c r="V65" s="36"/>
-      <c r="W65" s="36"/>
+      <c r="W65" s="36">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
       <c r="X65" s="36"/>
       <c r="Y65" s="36"/>
       <c r="Z65" s="36"/>
@@ -7021,37 +7234,43 @@
       <c r="H66" s="36"/>
       <c r="I66" s="36"/>
       <c r="J66" s="75">
-        <f t="shared" si="40"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="K66" s="36"/>
       <c r="L66" s="75">
-        <f t="shared" si="41"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M66" s="36"/>
       <c r="N66" s="36"/>
       <c r="O66" s="75">
-        <f t="shared" si="42"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="P66" s="75">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="Q66" s="75">
-        <f t="shared" si="44"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="R66" s="75">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="S66" s="36"/>
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="S66" s="36">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
       <c r="T66" s="36"/>
       <c r="U66" s="36"/>
       <c r="V66" s="36"/>
-      <c r="W66" s="36"/>
+      <c r="W66" s="36">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
       <c r="X66" s="36"/>
       <c r="Y66" s="36"/>
       <c r="Z66" s="36"/>
@@ -7079,123 +7298,123 @@
       <c r="F67" s="53"/>
       <c r="G67" s="53"/>
       <c r="H67" s="44">
-        <f t="shared" ref="H67:AK67" si="46">SUM(H63:H66)</f>
+        <f t="shared" ref="H67:AK67" si="58">SUM(H63:H66)</f>
         <v>0</v>
       </c>
       <c r="I67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="J67" s="76">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="K67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="L67" s="76">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="M67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="N67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="O67" s="76">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="P67" s="76">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="Q67" s="76">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="R67" s="76">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="S67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="T67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="U67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="V67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="W67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="X67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="Y67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="Z67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AA67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AB67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AC67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AD67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AE67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AF67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AG67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AH67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AI67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AJ67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AK67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AL67" s="151"/>
@@ -7211,123 +7430,123 @@
       <c r="F68" s="57"/>
       <c r="G68" s="57"/>
       <c r="H68" s="44">
-        <f t="shared" ref="H68:AK68" si="47">H17+H23+H34+H38+H46+H61+H67</f>
+        <f t="shared" ref="H68:AK68" si="59">H17+H23+H34+H38+H46+H61+H67</f>
         <v>0</v>
       </c>
       <c r="I68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="J68" s="76">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="K68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="L68" s="76">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="M68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="N68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="O68" s="76">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="P68" s="76">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="Q68" s="76">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="R68" s="76">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="S68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="T68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="U68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="V68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="W68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="X68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="Y68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="Z68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AA68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AB68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AC68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AD68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AE68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AF68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AG68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AH68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AI68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AJ68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AK68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AL68" s="151"/>
@@ -7347,12 +7566,12 @@
       <c r="H69" s="58"/>
       <c r="I69" s="58"/>
       <c r="J69" s="76">
-        <f t="shared" ref="J69:J76" si="48">H69+I69</f>
+        <f t="shared" ref="J69:J76" si="60">H69+I69</f>
         <v>0</v>
       </c>
       <c r="K69" s="58"/>
       <c r="L69" s="120">
-        <f t="shared" ref="L69:L75" si="49">J69-K69</f>
+        <f t="shared" ref="L69:L75" si="61">J69-K69</f>
         <v>0</v>
       </c>
       <c r="M69" s="36"/>
@@ -7362,25 +7581,28 @@
         <v>0</v>
       </c>
       <c r="P69" s="75">
-        <f t="shared" ref="P69:P72" si="50">K69-N69</f>
+        <f t="shared" ref="P69:P72" si="62">K69-N69</f>
         <v>0</v>
       </c>
       <c r="Q69" s="75">
-        <f t="shared" ref="Q69:Q72" si="51">M69+O69</f>
+        <f t="shared" ref="Q69:Q72" si="63">M69+O69</f>
         <v>0</v>
       </c>
       <c r="R69" s="75">
-        <f t="shared" ref="R69:R72" si="52">M69+N69+O69+P69</f>
-        <v>0</v>
-      </c>
-      <c r="S69" s="141">
-        <f t="shared" ref="S69:S72" si="53">SUM(T69:V69)</f>
+        <f t="shared" ref="R69:R72" si="64">M69+N69+O69+P69</f>
+        <v>0</v>
+      </c>
+      <c r="S69" s="36">
+        <f t="shared" ref="S69:S72" si="65">SUM(T69:V69)</f>
         <v>0</v>
       </c>
       <c r="T69" s="141"/>
       <c r="U69" s="141"/>
       <c r="V69" s="141"/>
-      <c r="W69" s="141"/>
+      <c r="W69" s="36">
+        <f t="shared" ref="W69:W72" si="66">SUM(X69:Y69)</f>
+        <v>0</v>
+      </c>
       <c r="X69" s="141"/>
       <c r="Y69" s="141"/>
       <c r="Z69" s="141"/>
@@ -7413,40 +7635,43 @@
       <c r="H70" s="58"/>
       <c r="I70" s="58"/>
       <c r="J70" s="76">
-        <f t="shared" si="48"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="K70" s="58"/>
       <c r="L70" s="120">
-        <f t="shared" si="49"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="M70" s="36"/>
       <c r="N70" s="36"/>
       <c r="O70" s="75">
-        <f t="shared" ref="O69:O72" si="54">L70-M70</f>
+        <f t="shared" ref="O69:O72" si="67">L70-M70</f>
         <v>0</v>
       </c>
       <c r="P70" s="75">
-        <f t="shared" si="50"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="Q70" s="75">
-        <f t="shared" si="51"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="R70" s="75">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="S70" s="141">
-        <f t="shared" si="53"/>
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="S70" s="36">
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="T70" s="141"/>
       <c r="U70" s="141"/>
       <c r="V70" s="141"/>
-      <c r="W70" s="141"/>
+      <c r="W70" s="36">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
       <c r="X70" s="141"/>
       <c r="Y70" s="141"/>
       <c r="Z70" s="141"/>
@@ -7476,40 +7701,43 @@
       <c r="H71" s="36"/>
       <c r="I71" s="36"/>
       <c r="J71" s="76">
-        <f t="shared" si="48"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="K71" s="36"/>
       <c r="L71" s="120">
-        <f t="shared" si="49"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="M71" s="36"/>
       <c r="N71" s="36"/>
       <c r="O71" s="75">
-        <f t="shared" si="54"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="P71" s="75">
-        <f t="shared" si="50"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="Q71" s="75">
-        <f t="shared" si="51"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="R71" s="75">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="S71" s="141">
-        <f t="shared" si="53"/>
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="S71" s="36">
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="T71" s="141"/>
       <c r="U71" s="141"/>
       <c r="V71" s="141"/>
-      <c r="W71" s="141"/>
+      <c r="W71" s="36">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
       <c r="X71" s="141"/>
       <c r="Y71" s="141"/>
       <c r="Z71" s="141"/>
@@ -7539,40 +7767,43 @@
       <c r="H72" s="36"/>
       <c r="I72" s="36"/>
       <c r="J72" s="76">
-        <f t="shared" si="48"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="K72" s="36"/>
       <c r="L72" s="120">
-        <f t="shared" si="49"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="M72" s="36"/>
       <c r="N72" s="36"/>
       <c r="O72" s="75">
-        <f t="shared" si="54"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="P72" s="75">
-        <f t="shared" si="50"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="Q72" s="75">
-        <f t="shared" si="51"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="R72" s="75">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="S72" s="141">
-        <f t="shared" si="53"/>
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="S72" s="36">
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="T72" s="141"/>
       <c r="U72" s="141"/>
       <c r="V72" s="141"/>
-      <c r="W72" s="141"/>
+      <c r="W72" s="36">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
       <c r="X72" s="141"/>
       <c r="Y72" s="141"/>
       <c r="Z72" s="141"/>
@@ -7602,112 +7833,112 @@
       <c r="H73" s="44"/>
       <c r="I73" s="44"/>
       <c r="J73" s="76">
-        <f t="shared" si="48"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="K73" s="44"/>
       <c r="L73" s="121">
-        <f t="shared" si="49"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="M73" s="122">
-        <f t="shared" ref="M73:AK73" si="55">SUM(M74:M76)</f>
+        <f t="shared" ref="M73:AK73" si="68">SUM(M74:M76)</f>
         <v>0</v>
       </c>
       <c r="N73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="O73" s="76">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="P73" s="76">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="Q73" s="76">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="R73" s="76">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="S73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="T73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="U73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="V73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="W73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="X73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="Y73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="Z73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AA73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AB73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AC73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AD73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AE73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AF73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AG73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AH73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AI73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AJ73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AK73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AL73" s="151"/>
@@ -7725,40 +7956,43 @@
       <c r="H74" s="36"/>
       <c r="I74" s="36"/>
       <c r="J74" s="76">
-        <f t="shared" si="48"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="K74" s="36"/>
       <c r="L74" s="120">
-        <f t="shared" si="49"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="M74" s="36"/>
       <c r="N74" s="36"/>
       <c r="O74" s="75">
-        <f t="shared" ref="O74:O76" si="56">L74-M74</f>
+        <f t="shared" ref="O74:O76" si="69">L74-M74</f>
         <v>0</v>
       </c>
       <c r="P74" s="75">
-        <f t="shared" ref="P74:P76" si="57">K74-N74</f>
+        <f t="shared" ref="P74:P76" si="70">K74-N74</f>
         <v>0</v>
       </c>
       <c r="Q74" s="75">
-        <f t="shared" ref="Q74:Q76" si="58">M74+O74</f>
+        <f t="shared" ref="Q74:Q76" si="71">M74+O74</f>
         <v>0</v>
       </c>
       <c r="R74" s="75">
-        <f t="shared" ref="R74:R76" si="59">M74+N74+O74+P74</f>
-        <v>0</v>
-      </c>
-      <c r="S74" s="141">
-        <f t="shared" ref="S74:S76" si="60">SUM(T74:V74)</f>
+        <f t="shared" ref="R74:R76" si="72">M74+N74+O74+P74</f>
+        <v>0</v>
+      </c>
+      <c r="S74" s="36">
+        <f t="shared" ref="S74:S76" si="73">SUM(T74:V74)</f>
         <v>0</v>
       </c>
       <c r="T74" s="141"/>
       <c r="U74" s="141"/>
       <c r="V74" s="141"/>
-      <c r="W74" s="141"/>
+      <c r="W74" s="36">
+        <f t="shared" ref="W74:W76" si="74">SUM(X74:Y74)</f>
+        <v>0</v>
+      </c>
       <c r="X74" s="141"/>
       <c r="Y74" s="141"/>
       <c r="Z74" s="141"/>
@@ -7788,7 +8022,7 @@
       <c r="H75" s="36"/>
       <c r="I75" s="36"/>
       <c r="J75" s="76">
-        <f t="shared" si="48"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="K75" s="36"/>
@@ -7796,29 +8030,32 @@
       <c r="M75" s="36"/>
       <c r="N75" s="36"/>
       <c r="O75" s="75">
-        <f t="shared" si="56"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="P75" s="75">
-        <f t="shared" si="57"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="Q75" s="75">
-        <f t="shared" si="58"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="R75" s="75">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="S75" s="141">
-        <f t="shared" si="60"/>
+        <f t="shared" si="72"/>
+        <v>0</v>
+      </c>
+      <c r="S75" s="36">
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="T75" s="141"/>
       <c r="U75" s="141"/>
       <c r="V75" s="141"/>
-      <c r="W75" s="141"/>
+      <c r="W75" s="36">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
       <c r="X75" s="141"/>
       <c r="Y75" s="141"/>
       <c r="Z75" s="141"/>
@@ -7848,7 +8085,7 @@
       <c r="H76" s="36"/>
       <c r="I76" s="36"/>
       <c r="J76" s="76">
-        <f t="shared" si="48"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="K76" s="36"/>
@@ -7856,29 +8093,32 @@
       <c r="M76" s="36"/>
       <c r="N76" s="36"/>
       <c r="O76" s="75">
-        <f t="shared" si="56"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="P76" s="75">
-        <f t="shared" si="57"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="Q76" s="75">
-        <f t="shared" si="58"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="R76" s="75">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="S76" s="141">
-        <f t="shared" si="60"/>
+        <f t="shared" si="72"/>
+        <v>0</v>
+      </c>
+      <c r="S76" s="36">
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="T76" s="141"/>
       <c r="U76" s="141"/>
       <c r="V76" s="141"/>
-      <c r="W76" s="141"/>
+      <c r="W76" s="36">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
       <c r="X76" s="141"/>
       <c r="Y76" s="141"/>
       <c r="Z76" s="141"/>
@@ -7895,7 +8135,7 @@
       <c r="AK76" s="83"/>
       <c r="AL76" s="97"/>
     </row>
-    <row r="77" s="1" customFormat="1" ht="14" spans="1:38">
+    <row r="77" s="1" customFormat="1" ht="26" spans="1:38">
       <c r="A77" s="41"/>
       <c r="B77" s="42"/>
       <c r="C77" s="42"/>
@@ -7905,79 +8145,127 @@
       <c r="E77" s="54"/>
       <c r="F77" s="54"/>
       <c r="G77" s="54"/>
-      <c r="H77" s="44" t="e">
-        <f>H68+H69+H70+H71+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I77" s="44" t="e">
-        <f>I68+I69+I70+I71+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J77" s="123" t="e">
-        <f>J68+J69+J70+J71+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K77" s="44" t="e">
-        <f>K68+K69+K70+K71+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L77" s="124" t="e">
-        <f>L68+L69+L70+L71+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M77" s="124">
-        <f>M68+M69+M70+M71</f>
-        <v>0</v>
-      </c>
-      <c r="N77" s="124">
-        <f t="shared" ref="M77:S77" si="61">N68+N69+N70+N71</f>
-        <v>0</v>
-      </c>
-      <c r="O77" s="125">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="P77" s="124">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="Q77" s="124">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="R77" s="124">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="S77" s="122">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="T77" s="122"/>
-      <c r="U77" s="122"/>
-      <c r="V77" s="122"/>
-      <c r="W77" s="122"/>
-      <c r="X77" s="122"/>
-      <c r="Y77" s="122"/>
-      <c r="Z77" s="122">
-        <f>Z68+Z69+Z70+Z71</f>
-        <v>0</v>
-      </c>
-      <c r="AA77" s="122">
-        <f>AA68+AA69+AA70+AA71</f>
-        <v>0</v>
-      </c>
-      <c r="AB77" s="145"/>
-      <c r="AC77" s="145"/>
-      <c r="AD77" s="145"/>
-      <c r="AE77" s="145"/>
-      <c r="AF77" s="145"/>
-      <c r="AG77" s="145"/>
-      <c r="AH77" s="145"/>
-      <c r="AI77" s="145"/>
-      <c r="AJ77" s="145"/>
-      <c r="AK77" s="152"/>
-      <c r="AL77" s="153"/>
+      <c r="H77" s="44">
+        <f t="shared" ref="H77:AK77" si="75">H68+H69+H70+H71+H72+H73</f>
+        <v>0</v>
+      </c>
+      <c r="I77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="J77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="K77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="L77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="M77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="N77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="O77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="P77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="Q77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="R77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="S77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="T77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="U77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="V77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="W77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="X77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="Y77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="Z77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="AA77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="AB77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="AC77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="AD77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="AE77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="AF77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="AG77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="AH77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="AI77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="AJ77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="AK77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="AL77" s="152"/>
     </row>
     <row r="78" s="1" customFormat="1" ht="26" spans="1:38">
       <c r="A78" s="41"/>
@@ -8017,11 +8305,17 @@
         <f>N78+P78</f>
         <v>0</v>
       </c>
-      <c r="S78" s="122"/>
+      <c r="S78" s="44">
+        <f>SUM(T78:V78)</f>
+        <v>0</v>
+      </c>
       <c r="T78" s="122"/>
       <c r="U78" s="122"/>
       <c r="V78" s="122"/>
-      <c r="W78" s="122"/>
+      <c r="W78" s="122">
+        <f>SUM(X78:Y78)</f>
+        <v>0</v>
+      </c>
       <c r="X78" s="122"/>
       <c r="Y78" s="122"/>
       <c r="Z78" s="122"/>
@@ -8035,8 +8329,8 @@
       <c r="AH78" s="145"/>
       <c r="AI78" s="145"/>
       <c r="AJ78" s="145"/>
-      <c r="AK78" s="152"/>
-      <c r="AL78" s="153"/>
+      <c r="AK78" s="153"/>
+      <c r="AL78" s="152"/>
     </row>
     <row r="79" s="1" customFormat="1" ht="26" spans="1:38">
       <c r="A79" s="41"/>
@@ -8076,11 +8370,17 @@
         <f>Q79</f>
         <v>0</v>
       </c>
-      <c r="S79" s="122"/>
+      <c r="S79" s="44">
+        <f>SUM(T79:V79)</f>
+        <v>0</v>
+      </c>
       <c r="T79" s="122"/>
       <c r="U79" s="122"/>
       <c r="V79" s="122"/>
-      <c r="W79" s="122"/>
+      <c r="W79" s="122">
+        <f>SUM(X79:Y79)</f>
+        <v>0</v>
+      </c>
       <c r="X79" s="122"/>
       <c r="Y79" s="122"/>
       <c r="Z79" s="122"/>
@@ -8094,8 +8394,8 @@
       <c r="AH79" s="145"/>
       <c r="AI79" s="145"/>
       <c r="AJ79" s="145"/>
-      <c r="AK79" s="152"/>
-      <c r="AL79" s="153"/>
+      <c r="AK79" s="153"/>
+      <c r="AL79" s="152"/>
     </row>
     <row r="80" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A80" s="41"/>
@@ -8109,9 +8409,9 @@
       <c r="G80" s="54"/>
       <c r="H80" s="44"/>
       <c r="I80" s="44"/>
-      <c r="J80" s="123" t="e">
+      <c r="J80" s="123">
         <f>J6-J77-J78-J79</f>
-        <v>#REF!</v>
+        <v>0</v>
       </c>
       <c r="K80" s="44"/>
       <c r="L80" s="124"/>
@@ -8139,8 +8439,8 @@
       <c r="AH80" s="145"/>
       <c r="AI80" s="145"/>
       <c r="AJ80" s="145"/>
-      <c r="AK80" s="152"/>
-      <c r="AL80" s="153"/>
+      <c r="AK80" s="153"/>
+      <c r="AL80" s="152"/>
     </row>
     <row r="81" s="3" customFormat="1" ht="14" spans="1:38">
       <c r="A81" s="101"/>
@@ -8155,16 +8455,16 @@
       <c r="H81" s="105"/>
       <c r="I81" s="105"/>
       <c r="J81" s="105" t="e">
-        <f t="shared" ref="J81:M81" si="62">J80/J6</f>
-        <v>#REF!</v>
+        <f t="shared" ref="J81:M81" si="76">J80/J6</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="K81" s="105"/>
       <c r="L81" s="126" t="e">
-        <f t="shared" si="62"/>
+        <f t="shared" si="76"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M81" s="126" t="e">
-        <f t="shared" si="62"/>
+        <f t="shared" si="76"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N81" s="126"/>
@@ -8199,7 +8499,7 @@
       <c r="AK81" s="154"/>
       <c r="AL81" s="155"/>
     </row>
-    <row r="82" ht="14" spans="1:38">
+    <row r="82" spans="1:38">
       <c r="A82" s="106"/>
       <c r="B82" s="107"/>
       <c r="C82" s="107"/>
@@ -8221,8 +8521,13 @@
       <c r="O82" s="130"/>
       <c r="P82" s="130"/>
       <c r="Q82" s="130"/>
-      <c r="R82" s="130"/>
-      <c r="S82" s="130"/>
+      <c r="R82" s="130" t="s">
+        <v>64</v>
+      </c>
+      <c r="S82" s="130">
+        <f>S77+S78+S79</f>
+        <v>0</v>
+      </c>
       <c r="T82" s="130"/>
       <c r="U82" s="130"/>
       <c r="V82" s="130"/>
@@ -8243,7 +8548,7 @@
       <c r="AK82" s="148"/>
       <c r="AL82" s="156"/>
     </row>
-    <row r="83" ht="14" spans="1:38">
+    <row r="83" spans="1:38">
       <c r="A83" s="106"/>
       <c r="B83" s="107"/>
       <c r="C83" s="107"/>
